--- a/ig/ch-term/ch-vacd-vaccines-sct-targetdiseases-cm.xlsx
+++ b/ig/ch-term/ch-vacd-vaccines-sct-targetdiseases-cm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1795,6 +1795,24 @@
   </si>
   <si>
     <t>Live attenuated Mycobacterium bovis antigen only vaccine product in parenteral dose form</t>
+  </si>
+  <si>
+    <t>1345202008</t>
+  </si>
+  <si>
+    <t>Chikungunya virus antigen-containing vaccine product</t>
+  </si>
+  <si>
+    <t>111864006</t>
+  </si>
+  <si>
+    <t>Chikungunya fever (disorder)</t>
+  </si>
+  <si>
+    <t>1344967001</t>
+  </si>
+  <si>
+    <t>Live attenuated Chikungunya virus antigen</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E351"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -8046,6 +8064,40 @@
         <v>154</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B352" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C352" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D352" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E352" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B353" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C353" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D353" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E353" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
